--- a/UserScore/speechscore.xlsx
+++ b/UserScore/speechscore.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,6 +860,240 @@
       </c>
       <c r="X5" t="n">
         <v>87.09999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>O000000000O00000000O</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>715.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-03-21 17:56</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>438.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="N6" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="O6" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="X6" t="n">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>O000000000O00000000O</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-21 12:58</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8375676141</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Lifeline_girl</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-03-21 13:26</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="V8" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="W8" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="X8" t="n">
+        <v>76.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/UserScore/speechscore.xlsx
+++ b/UserScore/speechscore.xlsx
@@ -878,24 +878,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>715.3</v>
+        <v>782.3</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-21 17:56</t>
+          <t>2026-03-22 10:21</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>438.5</v>
+        <v>505.5</v>
       </c>
       <c r="J6" t="n">
-        <v>87.7</v>
+        <v>84.2</v>
       </c>
       <c r="K6" t="n">
         <v>91.2</v>
@@ -937,7 +937,7 @@
         <v>66.40000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>79.5</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="7">
@@ -956,27 +956,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>50.5</v>
+        <v>119.4</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-03-21 20:56</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-03-21 12:58</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>50.5</v>
       </c>
       <c r="X7" t="n">
-        <v>50.5</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="8">

--- a/UserScore/speechscore.xlsx
+++ b/UserScore/speechscore.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,36 +878,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>782.3</v>
+        <v>1677.1</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-22 10:21</t>
+          <t>2026-03-22 23:05</t>
         </is>
       </c>
       <c r="H6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>956.1999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>100</v>
+      </c>
+      <c r="L6" t="n">
         <v>6</v>
       </c>
-      <c r="I6" t="n">
-        <v>505.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
       <c r="M6" t="n">
-        <v>92.90000000000001</v>
+        <v>476.8</v>
       </c>
       <c r="N6" t="n">
-        <v>92.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="O6" t="n">
         <v>92.90000000000001</v>
@@ -925,19 +925,19 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>183.9</v>
+        <v>244.1</v>
       </c>
       <c r="V6" t="n">
-        <v>61.3</v>
+        <v>61</v>
       </c>
       <c r="W6" t="n">
         <v>66.40000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>78.2</v>
+        <v>79.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -956,27 +956,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>119.4</v>
+        <v>50.5</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-21 20:56</t>
+          <t>2026-03-21 12:58</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>68.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>68.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>68.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>50.5</v>
       </c>
       <c r="X7" t="n">
-        <v>59.7</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="8">
@@ -1094,6 +1094,84 @@
       </c>
       <c r="X8" t="n">
         <v>76.59999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8454054235</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Upskill</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>161.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:43</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="N9" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="O9" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>80.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/UserScore/speechscore.xlsx
+++ b/UserScore/speechscore.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,66 +878,66 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1677.1</v>
+        <v>3628.6</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-03-22 23:05</t>
+          <t>2026-03-27 05:01</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>956.1999999999999</v>
+        <v>1396.8</v>
       </c>
       <c r="J6" t="n">
-        <v>86.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="K6" t="n">
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
-        <v>476.8</v>
+        <v>885.8000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>79.5</v>
+        <v>80.5</v>
       </c>
       <c r="O6" t="n">
         <v>92.90000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>796.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>79.7</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U6" t="n">
-        <v>244.1</v>
+        <v>549.2</v>
       </c>
       <c r="V6" t="n">
         <v>61</v>
       </c>
       <c r="W6" t="n">
-        <v>66.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="X6" t="n">
-        <v>79.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -956,14 +956,14 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>50.5</v>
+        <v>234.7</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-03-21 12:58</t>
+          <t>2026-03-27 05:03</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -991,16 +991,16 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>184.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>61.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>61.4</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
@@ -1015,7 +1015,7 @@
         <v>50.5</v>
       </c>
       <c r="X7" t="n">
-        <v>50.5</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="8">
@@ -1034,66 +1034,66 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>76.59999999999999</v>
+        <v>602.9</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-03-21 13:26</t>
+          <t>2026-03-25 06:57</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>249.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>83.2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>95.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>116.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>76.59999999999999</v>
+        <v>145.5</v>
       </c>
       <c r="V8" t="n">
-        <v>76.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="W8" t="n">
         <v>76.59999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>76.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1172,6 +1172,786 @@
       </c>
       <c r="X9" t="n">
         <v>80.59999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8449546048</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>🪐 सर्वम ❄️</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-03-27 06:06</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="X10" t="n">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>6248553686</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Supreme2315</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>139</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-03-27 05:36</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="N11" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8487113041</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>𝓡𝓐𝓜𝓨𝓐</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>170.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-03-24 06:55</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="N12" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8318750444</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bhumi</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-03-24 07:54</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="R13" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="S13" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8113544293</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rahaf2009</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>350.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-03-26 18:51</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="K14" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>127</v>
+      </c>
+      <c r="N14" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="S14" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5863975234</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:51</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="N15" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="O15" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>82.90000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>7355568919</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Krodhmedatyapremmenischhalhumai</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>223</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:12</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>223</v>
+      </c>
+      <c r="V16" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8262536945</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1001817635995</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mahalaxmi</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>44</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-03-26 15:43</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>44</v>
+      </c>
+      <c r="R17" t="n">
+        <v>44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>44</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>595208871</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1003354035186</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Swtysanu</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:30</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="N18" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>58.9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>595208871</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1003205119561</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Swtysanu</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-03-27 08:33</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>92.09999999999999</v>
       </c>
     </row>
   </sheetData>
